--- a/quality_surveys/031_visibility_improvement_feedback_form--quality_surveys.xlsx
+++ b/quality_surveys/031_visibility_improvement_feedback_form--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'reported_as_completed',_'label':_'reported_as_completed'}</t>
+          <t>reported_as_completed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'reported_as_completed', 'label': 'Reported as completed'}</t>
+          <t>Reported as completed</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'reported_as_partially_completed',_'label':_'reported_as_partially_completed'}</t>
+          <t>reported_as_partially_completed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'reported_as_partially_completed', 'label': 'Reported as partially completed'}</t>
+          <t>Reported as partially completed</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'reported_as_incompleted',_'label':_'reported_as_incompleted'}</t>
+          <t>reported_as_incompleted</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'reported_as_incompleted', 'label': 'Reported as incompleted'}</t>
+          <t>Reported as incompleted</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'reported_as_completed',_'label':_'reported_as_completed'}</t>
+          <t>reported_as_completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'reported_as_completed', 'label': 'Reported as completed'}</t>
+          <t>Reported as completed</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'partially_reported_as_completed',_'label':_'partially_reported_as_completed'}</t>
+          <t>partially_reported_as_completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'partially_reported_as_completed', 'label': 'Partially reported as completed'}</t>
+          <t>Partially reported as completed</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_reported_as_completed',_'label':_'not_reported_as_completed'}</t>
+          <t>not_reported_as_completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_reported_as_completed', 'label': 'Not reported as completed'}</t>
+          <t>Not reported as completed</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_1',_'label':_'facility_1'}</t>
+          <t>facility_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility 1', 'label': 'Facility 1'}</t>
+          <t>Facility 1</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'facility_2',_'label':_'facility_2'}</t>
+          <t>facility_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Facility 2', 'label': 'Facility 2'}</t>
+          <t>Facility 2</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'facility_3',_'label':_'facility_3'}</t>
+          <t>facility_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Facility 3', 'label': 'Facility 3'}</t>
+          <t>Facility 3</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_1',_'label':_'facility_1'}</t>
+          <t>facility_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility 1', 'label': 'Facility 1'}</t>
+          <t>Facility 1</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'facility_2',_'label':_'facility_2'}</t>
+          <t>facility_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Facility 2', 'label': 'Facility 2'}</t>
+          <t>Facility 2</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'facility_4',_'label':_'facility_4'}</t>
+          <t>facility_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Facility 4', 'label': 'Facility 4'}</t>
+          <t>Facility 4</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_1',_'label':_'facility_1'}</t>
+          <t>facility_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility 1', 'label': 'Facility 1'}</t>
+          <t>Facility 1</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'facility_2',_'label':_'facility_2'}</t>
+          <t>facility_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Facility 2', 'label': 'Facility 2'}</t>
+          <t>Facility 2</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'facility_3',_'label':_'facility_3'}</t>
+          <t>facility_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Facility 3', 'label': 'Facility 3'}</t>
+          <t>Facility 3</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'facility_5',_'label':_'facility_5'}</t>
+          <t>facility_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Facility 5', 'label': 'Facility 5'}</t>
+          <t>Facility 5</t>
         </is>
       </c>
     </row>
